--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="58">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,56 +50,149 @@
     <t>Total Price</t>
   </si>
   <si>
+    <t>TAY1381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Alza 1.5 EZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 1,176.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>RM 1,000.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed Underwriting Vehicle Age </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>RM 972.50</t>
+  </si>
+  <si>
+    <t>Cover Type Third</t>
+  </si>
+  <si>
+    <t>RM 769.75</t>
+  </si>
+  <si>
+    <t>RM 693.77</t>
+  </si>
+  <si>
+    <t>NCG9826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda Jazz 1.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1497 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CVT AUTO 7 SP SEQUENTIAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VTEC FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,452.69</t>
+  </si>
+  <si>
+    <t>RM 1,514.43</t>
+  </si>
+  <si>
+    <t>RM 1,180.50</t>
+  </si>
+  <si>
+    <t>VL3046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda City 1.5 V </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V MY2014 </t>
+  </si>
+  <si>
+    <t>RM 1,599.06</t>
+  </si>
+  <si>
+    <t>RM 1,784.48</t>
+  </si>
+  <si>
+    <t>RM 1,583.75</t>
+  </si>
+  <si>
+    <t>RM 1,931.15</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
     <t>Reason</t>
-  </si>
-  <si>
-    <t>TAY1381</t>
-  </si>
-  <si>
-    <t>ERROR</t>
-  </si>
-  <si>
-    <t>Enquiry form not found on page</t>
-  </si>
-  <si>
-    <t>NCG9826</t>
-  </si>
-  <si>
-    <t>VL3046</t>
-  </si>
-  <si>
-    <t>PHS2981</t>
-  </si>
-  <si>
-    <t>WYN3837</t>
-  </si>
-  <si>
-    <t>VBY7199</t>
-  </si>
-  <si>
-    <t>NDD6099</t>
-  </si>
-  <si>
-    <t>CDR7577</t>
-  </si>
-  <si>
-    <t>ALM8454</t>
-  </si>
-  <si>
-    <t>VFH174</t>
-  </si>
-  <si>
-    <t>RS6686</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -110,6 +203,10 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -142,11 +239,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -487,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -541,7 +639,654 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -549,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -557,136 +1302,15 @@
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
+      <c r="B1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="39">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,25 +50,25 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>TAY1381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERODUA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Alza 1.5 EZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495 </t>
+    <t>PHS2981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota VIOS 1.5G </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1497 </t>
   </si>
   <si>
     <t xml:space="preserve">4 SP AUTOMATIC </t>
   </si>
   <si>
-    <t xml:space="preserve">EZ </t>
+    <t xml:space="preserve">G-NCP93R BEPGKE </t>
   </si>
   <si>
     <t xml:space="preserve">Takaful </t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Chubb </t>
   </si>
   <si>
-    <t>RM 1,000.64</t>
+    <t>RM 1,304.53</t>
   </si>
   <si>
     <t xml:space="preserve">Lonpac </t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">Tokio Marine </t>
   </si>
   <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
+    <t xml:space="preserve">Connection down / Connection timeout </t>
   </si>
   <si>
     <t xml:space="preserve">Zurich </t>
   </si>
   <si>
-    <t>RM 972.50</t>
+    <t>RM 1,326.89</t>
   </si>
   <si>
     <t>Cover Type Third</t>
@@ -123,63 +123,6 @@
   </si>
   <si>
     <t>RM 693.77</t>
-  </si>
-  <si>
-    <t>NCG9826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HONDA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honda Jazz 1.5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1497 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CVT AUTO 7 SP SEQUENTIAL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VTEC FACELIFT </t>
-  </si>
-  <si>
-    <t>RM 1,452.69</t>
-  </si>
-  <si>
-    <t>RM 1,514.43</t>
-  </si>
-  <si>
-    <t>RM 1,180.50</t>
-  </si>
-  <si>
-    <t>VL3046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honda City 1.5 V </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">V MY2014 </t>
-  </si>
-  <si>
-    <t>RM 1,599.06</t>
-  </si>
-  <si>
-    <t>RM 1,784.48</t>
-  </si>
-  <si>
-    <t>RM 1,583.75</t>
-  </si>
-  <si>
-    <t>RM 1,931.15</t>
   </si>
   <si>
     <t>Status</t>
@@ -585,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -905,388 +848,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
+  <autoFilter ref="A1:L8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1307,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="72">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,25 +50,25 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>VFH174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">035427 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1799 </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM 2WD MY18 </t>
+    <t>JQP2685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.5 ZHS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE ZHS </t>
   </si>
   <si>
     <t xml:space="preserve">Takaful </t>
@@ -83,115 +83,145 @@
     <t xml:space="preserve">- </t>
   </si>
   <si>
-    <t>RM 2,068.27</t>
+    <t>RM 1,212.36</t>
   </si>
   <si>
     <t xml:space="preserve">Chubb </t>
   </si>
   <si>
+    <t>RM 1,346.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>RM 1,105.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
     <t xml:space="preserve">No </t>
   </si>
   <si>
-    <t xml:space="preserve">Fail Call to VIX </t>
+    <t xml:space="preserve">Connection down / Connection timeout </t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
-    <t>RM 2,846.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle Details Can't Found </t>
-  </si>
-  <si>
     <t xml:space="preserve">Zurich </t>
   </si>
   <si>
-    <t>RM 2,216.61</t>
-  </si>
-  <si>
-    <t>RS6686</t>
+    <t>RM 1,262.91</t>
+  </si>
+  <si>
+    <t>Cover Type Third</t>
+  </si>
+  <si>
+    <t>RM 824.50</t>
+  </si>
+  <si>
+    <t>RM 743.05</t>
+  </si>
+  <si>
+    <t>BNR9936</t>
   </si>
   <si>
     <t xml:space="preserve">HONDA </t>
   </si>
   <si>
-    <t xml:space="preserve">Honda Civic 1.5 TC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1498 </t>
+    <t xml:space="preserve">Honda CR-V 2.0 4WD i-VTEC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1997 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4WD MY2013 FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 2,125.75</t>
+  </si>
+  <si>
+    <t>RM 1,930.96</t>
+  </si>
+  <si>
+    <t>RM 2,146.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
+  </si>
+  <si>
+    <t>RM 1,741.69</t>
+  </si>
+  <si>
+    <t>BPM4990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NISSAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan Serena S-Hybrid HW Star </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 </t>
   </si>
   <si>
     <t xml:space="preserve">CONTINUOUS VARIABLE </t>
   </si>
   <si>
-    <t xml:space="preserve">TC </t>
-  </si>
-  <si>
-    <t>RM 2,527.46</t>
-  </si>
-  <si>
-    <t>RM 2,753.24</t>
-  </si>
-  <si>
-    <t>RM 2,504.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
-  </si>
-  <si>
-    <t>RM 2,227.76</t>
-  </si>
-  <si>
-    <t>JQP2685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERODUA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Myvi 1.5 ZHS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE ZHS </t>
-  </si>
-  <si>
-    <t>RM 1,212.36</t>
-  </si>
-  <si>
-    <t>RM 1,346.51</t>
-  </si>
-  <si>
-    <t>RM 1,105.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referred due to NCD Response [000 - OK for successful NCD confirmation/Enquiry] [Motor UW HQ] </t>
-  </si>
-  <si>
-    <t>Cover Type Third</t>
-  </si>
-  <si>
-    <t>RM 824.50</t>
-  </si>
-  <si>
-    <t>RM 743.05</t>
+    <t xml:space="preserve">S-HYBRID HIGHWAY STAR (CKD) C26 </t>
+  </si>
+  <si>
+    <t>RM 2,204.08</t>
+  </si>
+  <si>
+    <t>RM 2,020.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle use does not match the use code </t>
+  </si>
+  <si>
+    <t>RM 1,801.36</t>
+  </si>
+  <si>
+    <t>PMJ2431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1298 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZi PREMIUM </t>
+  </si>
+  <si>
+    <t>RM 1,163.14</t>
+  </si>
+  <si>
+    <t>RM 1,295.33</t>
+  </si>
+  <si>
+    <t>RM 1,060.30</t>
+  </si>
+  <si>
+    <t>RM 1,287.50</t>
+  </si>
+  <si>
+    <t>RM 791.11</t>
+  </si>
+  <si>
+    <t>RM 713.00</t>
   </si>
   <si>
     <t>Status</t>
@@ -597,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -718,13 +748,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
         <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -750,7 +780,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -762,7 +792,7 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -788,19 +818,19 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" t="s">
         <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -843,31 +873,31 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>21</v>
@@ -876,71 +906,71 @@
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="J8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
         <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
@@ -952,71 +982,71 @@
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
@@ -1028,109 +1058,109 @@
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
         <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
         <v>20</v>
@@ -1147,145 +1177,145 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="L15" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" t="s">
-        <v>57</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" t="s">
-        <v>22</v>
-      </c>
       <c r="L17" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>21</v>
@@ -1294,11 +1324,277 @@
         <v>22</v>
       </c>
       <c r="L18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>59</v>
       </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
+        <v>47</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
+  <autoFilter ref="A1:L25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1319,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="46">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,25 +50,25 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>JQP2685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERODUA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Myvi 1.5 ZHS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE ZHS </t>
+    <t>BNR9936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda CR-V 2.0 4WD i-VTEC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1997 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4WD MY2013 FACELIFT </t>
   </si>
   <si>
     <t xml:space="preserve">Takaful </t>
@@ -83,145 +83,67 @@
     <t xml:space="preserve">- </t>
   </si>
   <si>
-    <t>RM 1,212.36</t>
+    <t>RM 2,125.75</t>
   </si>
   <si>
     <t xml:space="preserve">Chubb </t>
   </si>
   <si>
-    <t>RM 1,346.51</t>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Failure, Web Service Down </t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t xml:space="preserve">Lonpac </t>
   </si>
   <si>
-    <t>RM 1,105.18</t>
+    <t>RM 2,146.72</t>
   </si>
   <si>
     <t xml:space="preserve">Tokio Marine </t>
   </si>
   <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connection down / Connection timeout </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zurich </t>
   </si>
   <si>
-    <t>RM 1,262.91</t>
-  </si>
-  <si>
-    <t>Cover Type Third</t>
-  </si>
-  <si>
-    <t>RM 824.50</t>
-  </si>
-  <si>
-    <t>RM 743.05</t>
-  </si>
-  <si>
-    <t>BNR9936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HONDA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honda CR-V 2.0 4WD i-VTEC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1997 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4WD MY2013 FACELIFT </t>
-  </si>
-  <si>
-    <t>RM 2,125.75</t>
-  </si>
-  <si>
-    <t>RM 1,930.96</t>
-  </si>
-  <si>
-    <t>RM 2,146.72</t>
+    <t>RM 1,741.69</t>
+  </si>
+  <si>
+    <t>BPM4990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NISSAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan Serena S-Hybrid HW Star </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-HYBRID HIGHWAY STAR (CKD) C26 </t>
+  </si>
+  <si>
+    <t>RM 2,204.08</t>
+  </si>
+  <si>
+    <t>RM 2,020.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle use does not match the use code </t>
   </si>
   <si>
     <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
   </si>
   <si>
-    <t>RM 1,741.69</t>
-  </si>
-  <si>
-    <t>BPM4990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NISSAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nissan Serena S-Hybrid HW Star </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-HYBRID HIGHWAY STAR (CKD) C26 </t>
-  </si>
-  <si>
-    <t>RM 2,204.08</t>
-  </si>
-  <si>
-    <t>RM 2,020.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle use does not match the use code </t>
-  </si>
-  <si>
     <t>RM 1,801.36</t>
-  </si>
-  <si>
-    <t>PMJ2431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Myvi 1.3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1298 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZi PREMIUM </t>
-  </si>
-  <si>
-    <t>RM 1,163.14</t>
-  </si>
-  <si>
-    <t>RM 1,295.33</t>
-  </si>
-  <si>
-    <t>RM 1,060.30</t>
-  </si>
-  <si>
-    <t>RM 1,287.50</t>
-  </si>
-  <si>
-    <t>RM 791.11</t>
-  </si>
-  <si>
-    <t>RM 713.00</t>
   </si>
   <si>
     <t>Status</t>
@@ -627,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -748,13 +670,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -780,7 +702,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -792,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -818,19 +740,19 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -856,7 +778,7 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
@@ -868,36 +790,36 @@
         <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>21</v>
@@ -906,36 +828,36 @@
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>21</v>
@@ -944,109 +866,109 @@
         <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
+      <c r="G9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" t="s">
+      <c r="G10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
-      </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="s">
+      <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s">
-        <v>43</v>
-      </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
@@ -1058,543 +980,11 @@
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="H12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" t="s">
-        <v>47</v>
-      </c>
-      <c r="L17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" t="s">
-        <v>47</v>
-      </c>
-      <c r="L22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" t="s">
-        <v>34</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" t="s">
-        <v>69</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:L11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1615,10 +1005,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="68">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,6 +50,81 @@
     <t>Total Price</t>
   </si>
   <si>
+    <t>JQP2685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.5 ZHS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE ZHS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 1,212.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>RM 1,346.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>RM 1,105.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Details Can't Found </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich Web Service is busy or down. Please try later </t>
+  </si>
+  <si>
+    <t>Cover Type Third</t>
+  </si>
+  <si>
+    <t>RM 824.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Failure, Web Service Down </t>
+  </si>
+  <si>
     <t>BNR9936</t>
   </si>
   <si>
@@ -71,46 +146,16 @@
     <t xml:space="preserve">4WD MY2013 FACELIFT </t>
   </si>
   <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
     <t>RM 2,125.75</t>
   </si>
   <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Failure, Web Service Down </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonpac </t>
+    <t>RM 1,930.96</t>
   </si>
   <si>
     <t>RM 2,146.72</t>
   </si>
   <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich </t>
-  </si>
-  <si>
-    <t>RM 1,741.69</t>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
   </si>
   <si>
     <t>BPM4990</t>
@@ -140,10 +185,31 @@
     <t xml:space="preserve">Vehicle use does not match the use code </t>
   </si>
   <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
-  </si>
-  <si>
-    <t>RM 1,801.36</t>
+    <t>PMJ2431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1298 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZi PREMIUM </t>
+  </si>
+  <si>
+    <t>RM 1,163.14</t>
+  </si>
+  <si>
+    <t>RM 1,295.33</t>
+  </si>
+  <si>
+    <t>RM 1,060.30</t>
+  </si>
+  <si>
+    <t>RM 791.11</t>
   </si>
   <si>
     <t>Status</t>
@@ -549,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -670,13 +736,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
         <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -702,7 +768,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -714,7 +780,7 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -740,19 +806,19 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -778,48 +844,48 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>21</v>
@@ -828,147 +894,147 @@
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
@@ -980,11 +1046,543 @@
         <v>22</v>
       </c>
       <c r="L11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
         <v>43</v>
       </c>
+      <c r="H12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
+        <v>47</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1005,10 +1603,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="210">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,93 +50,492 @@
     <t>Total Price</t>
   </si>
   <si>
+    <t>TDB9139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW X3 xDrive20d </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1995 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 SP AUTOMATIC STEPTRONIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xDrive20d (CKD) F25 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 1,733.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>RM 2,064.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>RM 1,852.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>RM 1,562.74</t>
+  </si>
+  <si>
+    <t>VCA5484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford Fiesta Sport 1.5L </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1498 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SP AUTOMATIC POWERSHIFT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPORT MY2013 </t>
+  </si>
+  <si>
+    <t>RM 1,131.63</t>
+  </si>
+  <si>
+    <t>RM 1,304.53</t>
+  </si>
+  <si>
+    <t>RM 1,031.56</t>
+  </si>
+  <si>
+    <t>RM 1,163.87</t>
+  </si>
+  <si>
+    <t>Cover Type Third</t>
+  </si>
+  <si>
+    <t>RM 769.75</t>
+  </si>
+  <si>
+    <t>RM 693.77</t>
+  </si>
+  <si>
+    <t>PLD1301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1298 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 SP MANUAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SX STANDARD </t>
+  </si>
+  <si>
+    <t>RM 1,001.68</t>
+  </si>
+  <si>
+    <t>RM 1,127.41</t>
+  </si>
+  <si>
+    <t>RM 913.05</t>
+  </si>
+  <si>
+    <t>RM 1,174.11</t>
+  </si>
+  <si>
+    <t>RM 681.60</t>
+  </si>
+  <si>
+    <t>RM 614.44</t>
+  </si>
+  <si>
+    <t>CCV939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda Odyssey 2.4 EXV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2356 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXV </t>
+  </si>
+  <si>
+    <t>RM 2,703.52</t>
+  </si>
+  <si>
+    <t>RM 2,787.27</t>
+  </si>
+  <si>
+    <t>RM 2,467.85</t>
+  </si>
+  <si>
+    <t>RM 2,812.82</t>
+  </si>
+  <si>
+    <t>TAY1381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Alza 1.5 EZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Failure, Web Service Down </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>RM 1,000.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed Underwriting Vehicle Age </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich Web Service is busy or down. Please try later </t>
+  </si>
+  <si>
+    <t>NCG9826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda Jazz 1.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1497 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CVT AUTO 7 SP SEQUENTIAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VTEC FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,452.69</t>
+  </si>
+  <si>
+    <t>RM 1,514.43</t>
+  </si>
+  <si>
+    <t>RM 1,180.50</t>
+  </si>
+  <si>
+    <t>VL3046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda City 1.5 V </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V MY2014 </t>
+  </si>
+  <si>
+    <t>RM 1,599.06</t>
+  </si>
+  <si>
+    <t>RM 1,784.48</t>
+  </si>
+  <si>
+    <t>RM 1,583.75</t>
+  </si>
+  <si>
+    <t>RM 1,931.15</t>
+  </si>
+  <si>
+    <t>PHS2981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota VIOS 1.5G </t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-NCP93R BEPGKE </t>
+  </si>
+  <si>
+    <t>RM 1,176.45</t>
+  </si>
+  <si>
+    <t>RM 1,326.89</t>
+  </si>
+  <si>
+    <t>WYN3837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIA RIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1396 </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">EX NA </t>
+  </si>
+  <si>
+    <t>RM 1,122.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail Call to VIX </t>
+  </si>
+  <si>
+    <t>RM 986.68</t>
+  </si>
+  <si>
+    <t>RM 763.74</t>
+  </si>
+  <si>
+    <t>VBY7199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 SP AUTOMATIC CONSTANTLY VARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V MY2014 FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,933.29</t>
+  </si>
+  <si>
+    <t>RM 2,147.76</t>
+  </si>
+  <si>
+    <t>RM 1,915.08</t>
+  </si>
+  <si>
+    <t>RM 2,204.28</t>
+  </si>
+  <si>
+    <t>NDD6099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.5 SE(A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,252.73</t>
+  </si>
+  <si>
+    <t>RM 1,430.47</t>
+  </si>
+  <si>
+    <t>RM 1,142.00</t>
+  </si>
+  <si>
+    <t>RM 1,311.21</t>
+  </si>
+  <si>
+    <t>RM 851.89</t>
+  </si>
+  <si>
+    <t>CDR7577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAZDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAZDA CX-5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1998 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2WD MID SPEC MY13 KE </t>
+  </si>
+  <si>
+    <t>RM 1,738.25</t>
+  </si>
+  <si>
+    <t>RM 1,815.39</t>
+  </si>
+  <si>
+    <t>ALM8454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISUZU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isuzu D-Max 4x2 Low Ride (M) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1898 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SP MANUAL MANUAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW RIDE MY16 RT FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 2,501.18</t>
+  </si>
+  <si>
+    <t>RM 2,684.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle use does not match the use code </t>
+  </si>
+  <si>
+    <t>RM 2,170.23</t>
+  </si>
+  <si>
+    <t>VFH174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proton X70 Premium 2WD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1799 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 SP AUTOMATIC DUAL CLUTCH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM 2WD MY18 </t>
+  </si>
+  <si>
+    <t>RM 2,288.93</t>
+  </si>
+  <si>
+    <t>RM 2,846.16</t>
+  </si>
+  <si>
+    <t>RS6686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda Civic 1.5 TC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC </t>
+  </si>
+  <si>
+    <t>RM 2,527.46</t>
+  </si>
+  <si>
+    <t>RM 2,753.24</t>
+  </si>
+  <si>
+    <t>RM 2,504.08</t>
+  </si>
+  <si>
+    <t>RM 2,227.76</t>
+  </si>
+  <si>
     <t>JQP2685</t>
   </si>
   <si>
-    <t xml:space="preserve">PERODUA </t>
-  </si>
-  <si>
     <t xml:space="preserve">Perodua Myvi 1.5 ZHS </t>
   </si>
   <si>
-    <t xml:space="preserve">2014 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
     <t xml:space="preserve">SE ZHS </t>
   </si>
   <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
     <t>RM 1,212.36</t>
   </si>
   <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
     <t>RM 1,346.51</t>
   </si>
   <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
     <t>RM 1,105.18</t>
   </si>
   <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle Details Can't Found </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich Web Service is busy or down. Please try later </t>
-  </si>
-  <si>
-    <t>Cover Type Third</t>
+    <t>RM 1,262.91</t>
   </si>
   <si>
     <t>RM 824.50</t>
   </si>
   <si>
-    <t xml:space="preserve">System Failure, Web Service Down </t>
+    <t>RM 743.05</t>
   </si>
   <si>
     <t>BNR9936</t>
   </si>
   <si>
-    <t xml:space="preserve">HONDA </t>
-  </si>
-  <si>
     <t xml:space="preserve">Honda CR-V 2.0 4WD i-VTEC </t>
   </si>
   <si>
-    <t xml:space="preserve">2016 </t>
-  </si>
-  <si>
     <t xml:space="preserve">1997 </t>
   </si>
   <si>
@@ -155,7 +554,7 @@
     <t>RM 2,146.72</t>
   </si>
   <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
+    <t>RM 1,741.69</t>
   </si>
   <si>
     <t>BPM4990</t>
@@ -167,12 +566,6 @@
     <t xml:space="preserve">Nissan Serena S-Hybrid HW Star </t>
   </si>
   <si>
-    <t xml:space="preserve">2018 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
-  </si>
-  <si>
     <t xml:space="preserve">S-HYBRID HIGHWAY STAR (CKD) C26 </t>
   </si>
   <si>
@@ -182,21 +575,12 @@
     <t>RM 2,020.47</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicle use does not match the use code </t>
+    <t>RM 1,801.36</t>
   </si>
   <si>
     <t>PMJ2431</t>
   </si>
   <si>
-    <t xml:space="preserve">Perodua Myvi 1.3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1298 </t>
-  </si>
-  <si>
     <t xml:space="preserve">EZi PREMIUM </t>
   </si>
   <si>
@@ -209,7 +593,49 @@
     <t>RM 1,060.30</t>
   </si>
   <si>
+    <t>RM 1,287.50</t>
+  </si>
+  <si>
     <t>RM 791.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referred due to NCD Response [000 - OK for successful NCD confirmation/Enquiry] [Motor UW HQ] </t>
+  </si>
+  <si>
+    <t>AHA430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota VIOS 1.5E </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-NCP93R BEPRKE </t>
+  </si>
+  <si>
+    <t>VNJ857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda City 1.5 (A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 SP AUTOMATIC CONSTANTLY VARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E MY2014 FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,747.61</t>
+  </si>
+  <si>
+    <t>RM 1,945.94</t>
+  </si>
+  <si>
+    <t>RM 1,731.01</t>
+  </si>
+  <si>
+    <t>RM 2,039.10</t>
   </si>
   <si>
     <t>Status</t>
@@ -615,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -812,80 +1238,80 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
         <v>29</v>
-      </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>21</v>
@@ -894,454 +1320,454 @@
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
         <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
         <v>41</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
         <v>42</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="J11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
         <v>43</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
         <v>48</v>
       </c>
-      <c r="B14" t="s">
+      <c r="G14" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
         <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
+      <c r="G15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
         <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
+      <c r="G16" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
         <v>41</v>
       </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="L16" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" t="s">
+      <c r="G17" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" t="s">
-        <v>53</v>
       </c>
       <c r="H17" t="s">
         <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
         <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>58</v>
       </c>
       <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
         <v>59</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>60</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
       </c>
       <c r="G19" t="s">
         <v>61</v>
       </c>
       <c r="H19" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>21</v>
@@ -1350,36 +1776,36 @@
         <v>22</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>58</v>
       </c>
       <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
         <v>59</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>60</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
       </c>
       <c r="G20" t="s">
         <v>61</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>21</v>
@@ -1388,33 +1814,33 @@
         <v>22</v>
       </c>
       <c r="L20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
         <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>58</v>
       </c>
       <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
         <v>59</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>60</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
       </c>
       <c r="G21" t="s">
         <v>61</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
         <v>20</v>
@@ -1426,163 +1852,3013 @@
         <v>22</v>
       </c>
       <c r="L21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="K22" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L22" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L23" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G24" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="L24" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K25" t="s">
+        <v>77</v>
+      </c>
+      <c r="L25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" t="s">
+        <v>73</v>
+      </c>
+      <c r="L27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
         <v>57</v>
       </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30" t="s">
+        <v>76</v>
+      </c>
+      <c r="L30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" t="s">
         <v>60</v>
       </c>
-      <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="G32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" t="s">
+        <v>98</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K38" t="s">
+        <v>76</v>
+      </c>
+      <c r="L38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" t="s">
+        <v>98</v>
+      </c>
+      <c r="H39" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" t="s">
+        <v>98</v>
+      </c>
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" t="s">
+        <v>98</v>
+      </c>
+      <c r="H41" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" t="s">
+        <v>104</v>
+      </c>
+      <c r="F42" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" t="s">
+        <v>106</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G43" t="s">
+        <v>106</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K43" t="s">
+        <v>108</v>
+      </c>
+      <c r="L43" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" t="s">
+        <v>105</v>
+      </c>
+      <c r="G44" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G45" t="s">
+        <v>106</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" t="s">
+        <v>112</v>
+      </c>
+      <c r="E46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46" t="s">
+        <v>113</v>
+      </c>
+      <c r="G46" t="s">
+        <v>114</v>
+      </c>
+      <c r="H46" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" t="s">
+        <v>113</v>
+      </c>
+      <c r="G47" t="s">
+        <v>114</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" t="s">
+        <v>22</v>
+      </c>
+      <c r="L47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" t="s">
+        <v>113</v>
+      </c>
+      <c r="G48" t="s">
+        <v>114</v>
+      </c>
+      <c r="H48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" t="s">
+        <v>113</v>
+      </c>
+      <c r="G49" t="s">
+        <v>114</v>
+      </c>
+      <c r="H49" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" t="s">
+        <v>120</v>
+      </c>
+      <c r="D50" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" t="s">
+        <v>70</v>
+      </c>
+      <c r="G50" t="s">
+        <v>122</v>
+      </c>
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s">
+        <v>22</v>
+      </c>
+      <c r="L50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" t="s">
+        <v>122</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" t="s">
+        <v>122</v>
+      </c>
+      <c r="H52" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s">
+        <v>22</v>
+      </c>
+      <c r="L52" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G53" t="s">
+        <v>122</v>
+      </c>
+      <c r="H53" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s">
+        <v>22</v>
+      </c>
+      <c r="L53" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G54" t="s">
+        <v>122</v>
+      </c>
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" t="s">
+        <v>41</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s">
+        <v>22</v>
+      </c>
+      <c r="L54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" t="s">
+        <v>130</v>
+      </c>
+      <c r="D55" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" t="s">
+        <v>131</v>
+      </c>
+      <c r="F55" t="s">
+        <v>105</v>
+      </c>
+      <c r="G55" t="s">
+        <v>132</v>
+      </c>
+      <c r="H55" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K55" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" t="s">
+        <v>131</v>
+      </c>
+      <c r="F56" t="s">
+        <v>105</v>
+      </c>
+      <c r="G56" t="s">
+        <v>132</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" t="s">
+        <v>8</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K56" t="s">
+        <v>108</v>
+      </c>
+      <c r="L56" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" t="s">
+        <v>131</v>
+      </c>
+      <c r="F57" t="s">
+        <v>105</v>
+      </c>
+      <c r="G57" t="s">
+        <v>132</v>
+      </c>
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" t="s">
+        <v>131</v>
+      </c>
+      <c r="F58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G58" t="s">
+        <v>132</v>
+      </c>
+      <c r="H58" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" t="s">
+        <v>139</v>
+      </c>
+      <c r="F59" t="s">
+        <v>140</v>
+      </c>
+      <c r="G59" t="s">
+        <v>141</v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" t="s">
+        <v>139</v>
+      </c>
+      <c r="F60" t="s">
+        <v>140</v>
+      </c>
+      <c r="G60" t="s">
+        <v>141</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s">
+        <v>22</v>
+      </c>
+      <c r="L60" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" t="s">
+        <v>139</v>
+      </c>
+      <c r="F61" t="s">
+        <v>140</v>
+      </c>
+      <c r="G61" t="s">
+        <v>141</v>
+      </c>
+      <c r="H61" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K61" t="s">
+        <v>144</v>
+      </c>
+      <c r="L61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" t="s">
+        <v>137</v>
+      </c>
+      <c r="D62" t="s">
+        <v>138</v>
+      </c>
+      <c r="E62" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" t="s">
+        <v>140</v>
+      </c>
+      <c r="G62" t="s">
+        <v>141</v>
+      </c>
+      <c r="H62" t="s">
+        <v>28</v>
+      </c>
+      <c r="I62" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K62" t="s">
+        <v>22</v>
+      </c>
+      <c r="L62" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" t="s">
+        <v>150</v>
+      </c>
+      <c r="F63" t="s">
+        <v>151</v>
+      </c>
+      <c r="G63" t="s">
+        <v>152</v>
+      </c>
+      <c r="H63" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K63" t="s">
+        <v>73</v>
+      </c>
+      <c r="L63" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" t="s">
+        <v>151</v>
+      </c>
+      <c r="G64" t="s">
+        <v>152</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" t="s">
+        <v>8</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s">
+        <v>22</v>
+      </c>
+      <c r="L64" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" t="s">
+        <v>147</v>
+      </c>
+      <c r="C65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" t="s">
+        <v>151</v>
+      </c>
+      <c r="G65" t="s">
+        <v>152</v>
+      </c>
+      <c r="H65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s">
+        <v>22</v>
+      </c>
+      <c r="L65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" t="s">
+        <v>148</v>
+      </c>
+      <c r="D66" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" t="s">
+        <v>151</v>
+      </c>
+      <c r="G66" t="s">
+        <v>152</v>
+      </c>
+      <c r="H66" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K66" t="s">
+        <v>73</v>
+      </c>
+      <c r="L66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" t="s">
+        <v>156</v>
+      </c>
+      <c r="D67" t="s">
+        <v>157</v>
+      </c>
+      <c r="E67" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" t="s">
-        <v>36</v>
-      </c>
-      <c r="L25" t="s">
-        <v>31</v>
+      <c r="F67" t="s">
+        <v>60</v>
+      </c>
+      <c r="G67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s">
+        <v>22</v>
+      </c>
+      <c r="L67" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" t="s">
+        <v>60</v>
+      </c>
+      <c r="G68" t="s">
+        <v>158</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" t="s">
+        <v>8</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s">
+        <v>22</v>
+      </c>
+      <c r="L68" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" t="s">
+        <v>156</v>
+      </c>
+      <c r="D69" t="s">
+        <v>157</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" t="s">
+        <v>60</v>
+      </c>
+      <c r="G69" t="s">
+        <v>158</v>
+      </c>
+      <c r="H69" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s">
+        <v>22</v>
+      </c>
+      <c r="L69" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" t="s">
+        <v>156</v>
+      </c>
+      <c r="D70" t="s">
+        <v>157</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70" t="s">
+        <v>60</v>
+      </c>
+      <c r="G70" t="s">
+        <v>158</v>
+      </c>
+      <c r="H70" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s">
+        <v>22</v>
+      </c>
+      <c r="L70" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>163</v>
+      </c>
+      <c r="B71" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>69</v>
+      </c>
+      <c r="F71" t="s">
+        <v>70</v>
+      </c>
+      <c r="G71" t="s">
+        <v>165</v>
+      </c>
+      <c r="H71" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s">
+        <v>22</v>
+      </c>
+      <c r="L71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" t="s">
+        <v>164</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="s">
+        <v>69</v>
+      </c>
+      <c r="F72" t="s">
+        <v>70</v>
+      </c>
+      <c r="G72" t="s">
+        <v>165</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" t="s">
+        <v>69</v>
+      </c>
+      <c r="F73" t="s">
+        <v>70</v>
+      </c>
+      <c r="G73" t="s">
+        <v>165</v>
+      </c>
+      <c r="H73" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" t="s">
+        <v>70</v>
+      </c>
+      <c r="G74" t="s">
+        <v>165</v>
+      </c>
+      <c r="H74" t="s">
+        <v>28</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" t="s">
+        <v>164</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" t="s">
+        <v>69</v>
+      </c>
+      <c r="F75" t="s">
+        <v>70</v>
+      </c>
+      <c r="G75" t="s">
+        <v>165</v>
+      </c>
+      <c r="H75" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" t="s">
+        <v>41</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s">
+        <v>22</v>
+      </c>
+      <c r="L75" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>163</v>
+      </c>
+      <c r="B76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>69</v>
+      </c>
+      <c r="F76" t="s">
+        <v>70</v>
+      </c>
+      <c r="G76" t="s">
+        <v>165</v>
+      </c>
+      <c r="H76" t="s">
+        <v>28</v>
+      </c>
+      <c r="I76" t="s">
+        <v>41</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s">
+        <v>22</v>
+      </c>
+      <c r="L76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" t="s">
+        <v>173</v>
+      </c>
+      <c r="D77" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77" t="s">
+        <v>174</v>
+      </c>
+      <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
+        <v>176</v>
+      </c>
+      <c r="H77" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s">
+        <v>22</v>
+      </c>
+      <c r="L77" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" t="s">
+        <v>57</v>
+      </c>
+      <c r="C78" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" t="s">
+        <v>89</v>
+      </c>
+      <c r="E78" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
+        <v>176</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" t="s">
+        <v>8</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s">
+        <v>22</v>
+      </c>
+      <c r="L78" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" t="s">
+        <v>173</v>
+      </c>
+      <c r="D79" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
+        <v>176</v>
+      </c>
+      <c r="H79" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s">
+        <v>22</v>
+      </c>
+      <c r="L79" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>172</v>
+      </c>
+      <c r="B80" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" t="s">
+        <v>173</v>
+      </c>
+      <c r="D80" t="s">
+        <v>89</v>
+      </c>
+      <c r="E80" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
+        <v>176</v>
+      </c>
+      <c r="H80" t="s">
+        <v>28</v>
+      </c>
+      <c r="I80" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s">
+        <v>22</v>
+      </c>
+      <c r="L80" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" t="s">
+        <v>183</v>
+      </c>
+      <c r="D81" t="s">
+        <v>112</v>
+      </c>
+      <c r="E81" t="s">
+        <v>174</v>
+      </c>
+      <c r="F81" t="s">
+        <v>60</v>
+      </c>
+      <c r="G81" t="s">
+        <v>184</v>
+      </c>
+      <c r="H81" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s">
+        <v>22</v>
+      </c>
+      <c r="L81" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" t="s">
+        <v>183</v>
+      </c>
+      <c r="D82" t="s">
+        <v>112</v>
+      </c>
+      <c r="E82" t="s">
+        <v>174</v>
+      </c>
+      <c r="F82" t="s">
+        <v>60</v>
+      </c>
+      <c r="G82" t="s">
+        <v>184</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82" t="s">
+        <v>8</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" t="s">
+        <v>174</v>
+      </c>
+      <c r="F83" t="s">
+        <v>60</v>
+      </c>
+      <c r="G83" t="s">
+        <v>184</v>
+      </c>
+      <c r="H83" t="s">
+        <v>26</v>
+      </c>
+      <c r="I83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K83" t="s">
+        <v>144</v>
+      </c>
+      <c r="L83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>181</v>
+      </c>
+      <c r="B84" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" t="s">
+        <v>183</v>
+      </c>
+      <c r="D84" t="s">
+        <v>112</v>
+      </c>
+      <c r="E84" t="s">
+        <v>174</v>
+      </c>
+      <c r="F84" t="s">
+        <v>60</v>
+      </c>
+      <c r="G84" t="s">
+        <v>184</v>
+      </c>
+      <c r="H84" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K84" t="s">
+        <v>22</v>
+      </c>
+      <c r="L84" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" t="s">
+        <v>45</v>
+      </c>
+      <c r="C85" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" t="s">
+        <v>121</v>
+      </c>
+      <c r="E85" t="s">
+        <v>47</v>
+      </c>
+      <c r="F85" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" t="s">
+        <v>189</v>
+      </c>
+      <c r="H85" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K85" t="s">
+        <v>22</v>
+      </c>
+      <c r="L85" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" t="s">
+        <v>121</v>
+      </c>
+      <c r="E86" t="s">
+        <v>47</v>
+      </c>
+      <c r="F86" t="s">
+        <v>70</v>
+      </c>
+      <c r="G86" t="s">
+        <v>189</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K86" t="s">
+        <v>22</v>
+      </c>
+      <c r="L86" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>188</v>
+      </c>
+      <c r="B87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" t="s">
+        <v>46</v>
+      </c>
+      <c r="D87" t="s">
+        <v>121</v>
+      </c>
+      <c r="E87" t="s">
+        <v>47</v>
+      </c>
+      <c r="F87" t="s">
+        <v>70</v>
+      </c>
+      <c r="G87" t="s">
+        <v>189</v>
+      </c>
+      <c r="H87" t="s">
+        <v>26</v>
+      </c>
+      <c r="I87" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K87" t="s">
+        <v>22</v>
+      </c>
+      <c r="L87" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>188</v>
+      </c>
+      <c r="B88" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" t="s">
+        <v>46</v>
+      </c>
+      <c r="D88" t="s">
+        <v>121</v>
+      </c>
+      <c r="E88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" t="s">
+        <v>189</v>
+      </c>
+      <c r="H88" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K88" t="s">
+        <v>22</v>
+      </c>
+      <c r="L88" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" t="s">
+        <v>46</v>
+      </c>
+      <c r="D89" t="s">
+        <v>121</v>
+      </c>
+      <c r="E89" t="s">
+        <v>47</v>
+      </c>
+      <c r="F89" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" t="s">
+        <v>189</v>
+      </c>
+      <c r="H89" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" t="s">
+        <v>41</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K89" t="s">
+        <v>22</v>
+      </c>
+      <c r="L89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>188</v>
+      </c>
+      <c r="B90" t="s">
+        <v>45</v>
+      </c>
+      <c r="C90" t="s">
+        <v>46</v>
+      </c>
+      <c r="D90" t="s">
+        <v>121</v>
+      </c>
+      <c r="E90" t="s">
+        <v>47</v>
+      </c>
+      <c r="F90" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" t="s">
+        <v>189</v>
+      </c>
+      <c r="H90" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" t="s">
+        <v>41</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K90" t="s">
+        <v>195</v>
+      </c>
+      <c r="L90" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>196</v>
+      </c>
+      <c r="B91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" t="s">
+        <v>197</v>
+      </c>
+      <c r="D91" t="s">
+        <v>198</v>
+      </c>
+      <c r="E91" t="s">
+        <v>81</v>
+      </c>
+      <c r="F91" t="s">
+        <v>70</v>
+      </c>
+      <c r="G91" t="s">
+        <v>199</v>
+      </c>
+      <c r="H91" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s">
+        <v>22</v>
+      </c>
+      <c r="L91" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" t="s">
+        <v>96</v>
+      </c>
+      <c r="C92" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92" t="s">
+        <v>198</v>
+      </c>
+      <c r="E92" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" t="s">
+        <v>199</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" t="s">
+        <v>8</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s">
+        <v>22</v>
+      </c>
+      <c r="L92" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" t="s">
+        <v>96</v>
+      </c>
+      <c r="C93" t="s">
+        <v>197</v>
+      </c>
+      <c r="D93" t="s">
+        <v>198</v>
+      </c>
+      <c r="E93" t="s">
+        <v>81</v>
+      </c>
+      <c r="F93" t="s">
+        <v>70</v>
+      </c>
+      <c r="G93" t="s">
+        <v>199</v>
+      </c>
+      <c r="H93" t="s">
+        <v>26</v>
+      </c>
+      <c r="I93" t="s">
+        <v>20</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K93" t="s">
+        <v>76</v>
+      </c>
+      <c r="L93" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>196</v>
+      </c>
+      <c r="B94" t="s">
+        <v>96</v>
+      </c>
+      <c r="C94" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" t="s">
+        <v>198</v>
+      </c>
+      <c r="E94" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" t="s">
+        <v>199</v>
+      </c>
+      <c r="H94" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" t="s">
+        <v>20</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K94" t="s">
+        <v>77</v>
+      </c>
+      <c r="L94" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>196</v>
+      </c>
+      <c r="B95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" t="s">
+        <v>81</v>
+      </c>
+      <c r="F95" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" t="s">
+        <v>199</v>
+      </c>
+      <c r="H95" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95" t="s">
+        <v>41</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s">
+        <v>22</v>
+      </c>
+      <c r="L95" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C96" t="s">
+        <v>197</v>
+      </c>
+      <c r="D96" t="s">
+        <v>198</v>
+      </c>
+      <c r="E96" t="s">
+        <v>81</v>
+      </c>
+      <c r="F96" t="s">
+        <v>70</v>
+      </c>
+      <c r="G96" t="s">
+        <v>199</v>
+      </c>
+      <c r="H96" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" t="s">
+        <v>41</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K96" t="s">
+        <v>73</v>
+      </c>
+      <c r="L96" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" t="s">
+        <v>57</v>
+      </c>
+      <c r="C97" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" t="s">
+        <v>157</v>
+      </c>
+      <c r="E97" t="s">
+        <v>81</v>
+      </c>
+      <c r="F97" t="s">
+        <v>202</v>
+      </c>
+      <c r="G97" t="s">
+        <v>203</v>
+      </c>
+      <c r="H97" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s">
+        <v>22</v>
+      </c>
+      <c r="L97" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>200</v>
+      </c>
+      <c r="B98" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" t="s">
+        <v>201</v>
+      </c>
+      <c r="D98" t="s">
+        <v>157</v>
+      </c>
+      <c r="E98" t="s">
+        <v>81</v>
+      </c>
+      <c r="F98" t="s">
+        <v>202</v>
+      </c>
+      <c r="G98" t="s">
+        <v>203</v>
+      </c>
+      <c r="H98" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" t="s">
+        <v>8</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s">
+        <v>22</v>
+      </c>
+      <c r="L98" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" t="s">
+        <v>57</v>
+      </c>
+      <c r="C99" t="s">
+        <v>201</v>
+      </c>
+      <c r="D99" t="s">
+        <v>157</v>
+      </c>
+      <c r="E99" t="s">
+        <v>81</v>
+      </c>
+      <c r="F99" t="s">
+        <v>202</v>
+      </c>
+      <c r="G99" t="s">
+        <v>203</v>
+      </c>
+      <c r="H99" t="s">
+        <v>26</v>
+      </c>
+      <c r="I99" t="s">
+        <v>20</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s">
+        <v>22</v>
+      </c>
+      <c r="L99" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>200</v>
+      </c>
+      <c r="B100" t="s">
+        <v>57</v>
+      </c>
+      <c r="C100" t="s">
+        <v>201</v>
+      </c>
+      <c r="D100" t="s">
+        <v>157</v>
+      </c>
+      <c r="E100" t="s">
+        <v>81</v>
+      </c>
+      <c r="F100" t="s">
+        <v>202</v>
+      </c>
+      <c r="G100" t="s">
+        <v>203</v>
+      </c>
+      <c r="H100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" t="s">
+        <v>20</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K100" t="s">
+        <v>22</v>
+      </c>
+      <c r="L100" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:L100"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1603,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>67</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="72">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,64 +50,178 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>NDD6099</t>
+    <t>MCW3799</t>
   </si>
   <si>
     <t xml:space="preserve">PERODUA </t>
   </si>
   <si>
-    <t xml:space="preserve">Perodua Myvi 1.5 SE(A) </t>
+    <t xml:space="preserve">Perodua Bezza 1300 X (A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1329 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM X </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 1,145.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>RM 1,331.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>RM 1,133.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>RM 1,198.31</t>
+  </si>
+  <si>
+    <t>MCA2388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proton Saga 1.3 FL(A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1332 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL </t>
+  </si>
+  <si>
+    <t>RM 799.86</t>
+  </si>
+  <si>
+    <t>RM 917.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed Underwriting Vehicle Age </t>
+  </si>
+  <si>
+    <t>RM 889.38</t>
+  </si>
+  <si>
+    <t>Cover Type Third</t>
+  </si>
+  <si>
+    <t>RM 517.33</t>
+  </si>
+  <si>
+    <t>RM 568.07</t>
+  </si>
+  <si>
+    <t>BQT3130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda City RS e:HEV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1498 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 SP AUTOMATIC CONSTANTLY VARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS e:HEV MY21 GN6 </t>
+  </si>
+  <si>
+    <t>RM 3,270.17</t>
+  </si>
+  <si>
+    <t>RM 3,346.20</t>
+  </si>
+  <si>
+    <t>RM 3,240.33</t>
+  </si>
+  <si>
+    <t>RM 3,038.53</t>
+  </si>
+  <si>
+    <t>NDC7743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA MYVI 1.3 PREMIUM X(A) </t>
   </si>
   <si>
     <t xml:space="preserve">2015 </t>
   </si>
   <si>
-    <t xml:space="preserve">1495 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE FACELIFT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
-    <t>RM 1,252.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
-    <t>RM 1,430.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
-    <t>RM 1,142.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich </t>
-  </si>
-  <si>
-    <t>RM 1,311.21</t>
-  </si>
-  <si>
-    <t>Cover Type Third</t>
-  </si>
-  <si>
-    <t>RM 851.89</t>
+    <t xml:space="preserve">1298 </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM X MY11 M600 FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,122.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail Call to VIX </t>
+  </si>
+  <si>
+    <t>RM 1,023.48</t>
+  </si>
+  <si>
+    <t>RM 1,275.74</t>
+  </si>
+  <si>
+    <t>RM 763.74</t>
+  </si>
+  <si>
+    <t>RM 688.36</t>
   </si>
   <si>
     <t>Status</t>
@@ -513,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -710,13 +824,13 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -742,23 +856,745 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="L10" t="s">
         <v>31</v>
       </c>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -779,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="73">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">PERODUA </t>
   </si>
   <si>
-    <t xml:space="preserve">Perodua Bezza 1300 X (A) </t>
+    <t xml:space="preserve">PERODUA BEZZA PREMIUM X(A) </t>
   </si>
   <si>
     <t xml:space="preserve">2016 </t>
@@ -65,72 +65,75 @@
     <t xml:space="preserve">1329 </t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM X MY16 D63D </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 1,145.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail to call compliance link. Contact Your Marketer. </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>RM 1,133.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>RM 1,198.31</t>
+  </si>
+  <si>
+    <t>MCA2388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proton Saga 1.3 FL(A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1332 </t>
+  </si>
+  <si>
     <t xml:space="preserve">4 SP AUTOMATIC </t>
   </si>
   <si>
-    <t xml:space="preserve">PREMIUM X </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
-    <t>RM 1,145.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
-    <t>RM 1,331.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
-    <t>RM 1,133.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich </t>
-  </si>
-  <si>
-    <t>RM 1,198.31</t>
-  </si>
-  <si>
-    <t>MCA2388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proton Saga 1.3 FL(A) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1332 </t>
-  </si>
-  <si>
     <t xml:space="preserve">FL </t>
   </si>
   <si>
@@ -161,7 +164,7 @@
     <t xml:space="preserve">HONDA </t>
   </si>
   <si>
-    <t xml:space="preserve">Honda City RS e:HEV </t>
+    <t xml:space="preserve">HONDA CITY </t>
   </si>
   <si>
     <t xml:space="preserve">2022 </t>
@@ -170,18 +173,12 @@
     <t xml:space="preserve">1498 </t>
   </si>
   <si>
-    <t xml:space="preserve">1 SP AUTOMATIC CONSTANTLY VARI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS e:HEV MY21 GN6 </t>
+    <t xml:space="preserve">E:HEV RS MY21 GN6 </t>
   </si>
   <si>
     <t>RM 3,270.17</t>
   </si>
   <si>
-    <t>RM 3,346.20</t>
-  </si>
-  <si>
     <t>RM 3,240.33</t>
   </si>
   <si>
@@ -191,7 +188,7 @@
     <t>NDC7743</t>
   </si>
   <si>
-    <t xml:space="preserve">PERODUA MYVI 1.3 PREMIUM X(A) </t>
+    <t xml:space="preserve">Perodua Myvi 1.3 X(A) Premium </t>
   </si>
   <si>
     <t xml:space="preserve">2015 </t>
@@ -200,16 +197,13 @@
     <t xml:space="preserve">1298 </t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM X MY11 M600 FACELIFT </t>
+    <t xml:space="preserve">PREMIUM X FACELIFT </t>
   </si>
   <si>
     <t>RM 1,122.78</t>
   </si>
   <si>
-    <t xml:space="preserve">Fail Call to VIX </t>
+    <t>RM 1,295.33</t>
   </si>
   <si>
     <t>RM 1,023.48</t>
@@ -228,6 +222,15 @@
   </si>
   <si>
     <t>Reason</t>
+  </si>
+  <si>
+    <t>EABTJB7</t>
+  </si>
+  <si>
+    <t>NO_VEHICLE_INFO</t>
+  </si>
+  <si>
+    <t>Unable to retrieve your vehicle information</t>
   </si>
 </sst>
 </file>
@@ -748,13 +751,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -780,7 +783,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -792,7 +795,7 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -818,19 +821,19 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -888,10 +891,10 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -906,7 +909,7 @@
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -926,10 +929,10 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -944,7 +947,7 @@
         <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -964,25 +967,25 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1002,25 +1005,25 @@
         <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1040,10 +1043,10 @@
         <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
@@ -1058,7 +1061,7 @@
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1078,16 +1081,16 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>21</v>
@@ -1096,7 +1099,7 @@
         <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1116,16 +1119,16 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
         <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>21</v>
@@ -1134,27 +1137,27 @@
         <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
         <v>53</v>
@@ -1177,22 +1180,22 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
         <v>53</v>
@@ -1204,39 +1207,39 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
         <v>53</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -1248,65 +1251,65 @@
         <v>22</v>
       </c>
       <c r="L16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
         <v>53</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
         <v>53</v>
@@ -1324,30 +1327,30 @@
         <v>22</v>
       </c>
       <c r="L18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
         <v>59</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>60</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" t="s">
         <v>61</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" t="s">
-        <v>63</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -1362,30 +1365,30 @@
         <v>22</v>
       </c>
       <c r="L19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
         <v>59</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>60</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>63</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
@@ -1394,39 +1397,39 @@
         <v>8</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="L20" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
         <v>59</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>60</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" t="s">
         <v>61</v>
       </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" t="s">
-        <v>63</v>
-      </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
         <v>20</v>
@@ -1438,68 +1441,68 @@
         <v>22</v>
       </c>
       <c r="L21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
         <v>59</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>60</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" t="s">
         <v>61</v>
       </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" t="s">
-        <v>63</v>
-      </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
         <v>59</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>60</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" t="s">
         <v>61</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" t="s">
-        <v>63</v>
       </c>
       <c r="H23" t="s">
         <v>32</v>
@@ -1514,36 +1517,36 @@
         <v>22</v>
       </c>
       <c r="L23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
         <v>59</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>60</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" t="s">
         <v>61</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" t="s">
-        <v>63</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>21</v>
@@ -1552,36 +1555,36 @@
         <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
         <v>59</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>60</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s">
         <v>61</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" t="s">
-        <v>63</v>
       </c>
       <c r="H25" t="s">
         <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>21</v>
@@ -1590,7 +1593,7 @@
         <v>22</v>
       </c>
       <c r="L25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1602,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1615,10 +1618,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" t="s">
         <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="46">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,25 +50,25 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>MCW3799</t>
+    <t>JQA2210</t>
   </si>
   <si>
     <t xml:space="preserve">PERODUA </t>
   </si>
   <si>
-    <t xml:space="preserve">PERODUA BEZZA PREMIUM X(A) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1329 </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM X MY16 D63D </t>
+    <t xml:space="preserve">Perodua Alza 1.5(A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR BZ </t>
   </si>
   <si>
     <t xml:space="preserve">Takaful </t>
@@ -83,154 +83,73 @@
     <t xml:space="preserve">- </t>
   </si>
   <si>
-    <t>RM 1,145.29</t>
+    <t>RM 1,212.36</t>
   </si>
   <si>
     <t xml:space="preserve">Chubb </t>
   </si>
   <si>
+    <t>RM 1,031.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>RM 1,105.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
     <t xml:space="preserve">No </t>
   </si>
   <si>
-    <t xml:space="preserve">Fail to call compliance link. Contact Your Marketer. </t>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
-    <t>RM 1,133.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich </t>
-  </si>
-  <si>
-    <t>RM 1,198.31</t>
-  </si>
-  <si>
-    <t>MCA2388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proton Saga 1.3 FL(A) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1332 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL </t>
-  </si>
-  <si>
-    <t>RM 799.86</t>
-  </si>
-  <si>
-    <t>RM 917.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Failed Underwriting Vehicle Age </t>
-  </si>
-  <si>
-    <t>RM 889.38</t>
-  </si>
-  <si>
     <t>Cover Type Third</t>
   </si>
   <si>
-    <t>RM 517.33</t>
-  </si>
-  <si>
-    <t>RM 568.07</t>
-  </si>
-  <si>
-    <t>BQT3130</t>
+    <t>RM 824.50</t>
+  </si>
+  <si>
+    <t>PMH4872</t>
   </si>
   <si>
     <t xml:space="preserve">HONDA </t>
   </si>
   <si>
-    <t xml:space="preserve">HONDA CITY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1498 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">E:HEV RS MY21 GN6 </t>
-  </si>
-  <si>
-    <t>RM 3,270.17</t>
-  </si>
-  <si>
-    <t>RM 3,240.33</t>
-  </si>
-  <si>
-    <t>RM 3,038.53</t>
-  </si>
-  <si>
-    <t>NDC7743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Myvi 1.3 X(A) Premium </t>
+    <t xml:space="preserve">Honda HR-V 1.8 S </t>
   </si>
   <si>
     <t xml:space="preserve">2015 </t>
   </si>
   <si>
-    <t xml:space="preserve">1298 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM X FACELIFT </t>
-  </si>
-  <si>
-    <t>RM 1,122.78</t>
-  </si>
-  <si>
-    <t>RM 1,295.33</t>
-  </si>
-  <si>
-    <t>RM 1,023.48</t>
-  </si>
-  <si>
-    <t>RM 1,275.74</t>
-  </si>
-  <si>
-    <t>RM 763.74</t>
-  </si>
-  <si>
-    <t>RM 688.36</t>
+    <t xml:space="preserve">1799 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S </t>
+  </si>
+  <si>
+    <t>RM 1,738.63</t>
+  </si>
+  <si>
+    <t>RM 1,630.28</t>
+  </si>
+  <si>
+    <t>RM 1,815.39</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
     <t>Reason</t>
-  </si>
-  <si>
-    <t>EABTJB7</t>
-  </si>
-  <si>
-    <t>NO_VEHICLE_INFO</t>
-  </si>
-  <si>
-    <t>Unable to retrieve your vehicle information</t>
   </si>
 </sst>
 </file>
@@ -630,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -751,13 +670,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
         <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -783,7 +702,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -795,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -821,19 +740,19 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" t="s">
         <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -859,10 +778,10 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
         <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>21</v>
@@ -973,19 +892,19 @@
         <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
         <v>43</v>
-      </c>
-      <c r="L9" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1011,593 +930,23 @@
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" t="s">
         <v>31</v>
       </c>
-      <c r="L10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" t="s">
-        <v>31</v>
-      </c>
-      <c r="L22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" t="s">
-        <v>61</v>
-      </c>
-      <c r="H24" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" t="s">
-        <v>67</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1605,7 +954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1618,21 +967,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,113 +50,29 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>JQA2210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERODUA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Alza 1.5(A) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR BZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
-    <t>RM 1,212.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
-    <t>RM 1,031.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
-    <t>RM 1,105.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued but payment not acknowledged for more than 10 days! </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Cover Type Third</t>
-  </si>
-  <si>
-    <t>RM 824.50</t>
-  </si>
-  <si>
-    <t>PMH4872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HONDA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honda HR-V 1.8 S </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1799 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">S </t>
-  </si>
-  <si>
-    <t>RM 1,738.63</t>
-  </si>
-  <si>
-    <t>RM 1,630.28</t>
-  </si>
-  <si>
-    <t>RM 1,815.39</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
     <t>Reason</t>
+  </si>
+  <si>
+    <t>VAJ124</t>
+  </si>
+  <si>
+    <t>NO_VEHICLE_INFO</t>
+  </si>
+  <si>
+    <t>Unable to retrieve your vehicle information</t>
+  </si>
+  <si>
+    <t>VAH0124</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -167,10 +83,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -203,12 +115,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -549,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -603,350 +514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -954,7 +522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -962,15 +530,37 @@
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="147">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,13 +50,328 @@
     <t>Total Price</t>
   </si>
   <si>
+    <t>VMV4697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAMAHA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAMAHA NVX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE TRANSMISSION </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STANDARD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">System error, please contact IT support. </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Cover Type Third Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Failure, Web Service Down </t>
+  </si>
+  <si>
+    <t>JXQ6278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW IX xDRIVE40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT TRANSMISSION - 2 SP AUTOMATIC3 SP AUTOMATIC SPORTS MODE1 SP AUTOMATIC1 SP AUTOMATIC SINGLE CLUTCH1 SP AUTOMATIC CONVENTIONAL1 SP AUTOMATIC AUTOMATIC3 SP AUTOMATIC AUTOMATIC SPORT0 SP AUTOMATIC AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT VARIANT (SERIES) - GOOD CAT 400 PRO MY22GOOD CAT 500 ULTRA MY22M SPORT INSPIRING MY21 G08M SPORT IMPRESSIVE MY21 G08 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>Cover Type Private Car (Enhanced)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 2,707.92</t>
+  </si>
+  <si>
+    <t>QBH1286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAMAHA Y16ZR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SPEED MANUAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TECH ART DOXOU </t>
+  </si>
+  <si>
+    <t>MALAYSIA3187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MITSUBISHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi Triton VGT Athlete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2442 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SP AUTOMATIC SPORTS MODE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VGT ATHLETE MY19 L200 ENHANCED </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VEHICLE WITH REFERRED RISK,VEHICLE WITH REFERRED RISK </t>
+  </si>
+  <si>
+    <t>RM 4,445.23</t>
+  </si>
+  <si>
+    <t>VAY1881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota Hiace SLWB Window Van </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2755 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLWB WINDOW VAN GDH321R </t>
+  </si>
+  <si>
+    <t xml:space="preserve">webservice api error </t>
+  </si>
+  <si>
+    <t>RM 4,189.72</t>
+  </si>
+  <si>
+    <t>VPB4370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi I-MIEV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT VARIANT (SERIES) - CARGO URBAN EV EV ZE0AELXXFL </t>
+  </si>
+  <si>
+    <t>RM 1,351.65</t>
+  </si>
+  <si>
+    <t>JWC4641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audi E-Tron GT QUATTRO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT TRANSMISSION - 2 SP AUTOMATIC3 SP AUTOMATIC SPORTS MODE1 SP AUTOMATIC1 SP AUTOMATIC CONVENTIONAL2 SP AUTOMATIC DUAL CLUTCH1 SP AUTOMATIC SINGLE CLUTCH1 SP AUTOMATIC AUTOMATIC3 SP AUTOMATIC AUTOMATIC SPORT1 SP AUTOMATIC CONSTANTLY VARI0 SP AUTOMATIC AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT VARIANT (SERIES) - DYNAMIC STANDARD RANGE MY23STANDARD MY22PREMIUM EXTENDED RANGE MY23EXTENDED MY22EV MY19 ZE1EV MY19 ZE1 FACELIFTZEN R110 MY22 ZE50INTENS R135 MY22 ZE505 LITE MY22 NERWD MY23STANDARD RANGE MY23SE MY20 F56 FACELIFTSE RESOLUTE EDITION MY20 F56 FACELIFT5 PLUS MY22 NELONG RANGE AWD MY23PREMIUM MY23STANDARD RANGE (ENHANCED AUTOP MY23250 AMG LINE MY22 H243LONG RANGE AWD (ENHANCED AUTOP MY23STANDARD RANGE (FULL SELF-DRIV MY235 MAX MY22 NELONG RANGE MY23LONG RANGE AWD (FULL SELF-DRIV MY23BRABUS MY23350 MY22 X243P8 RECHARGE MY22eDRIVE35 SPORT MY22 G266 MAX RWD MY23 CELONG RANGE (ENHANCED AUTOPILOT MY23eDRIVE35 M SPORT MY22 G26LONG RANGE (FULL SELF-DRIVE) MY23PERFORMANCE MY236 MAX AWD MY23 CERECHARGE P8 MY23GT LINE MY22 CVPERFORMANCE (ENHANCED AUTOPILO MY23400 MY22 N293PERFORMANCE (FULL SELF-DRIVE) MY23eDRIVE40 M SPORT MY22 G26GT QUATTRO MY23eDRIVE40 M SPORT MY23 G60350+ AMG LINE MY22 V295xDRIVE50 MY21 I20500 4MATIC MY23 X294450+ AMG MY22 V297M60 MY21 I20MY2353 4MATIC+ AMG MY22 V295580 4MATIC MY23 X296xDRIVE60 M SPORT MY23 G70S MY23R MY23 </t>
+  </si>
+  <si>
+    <t>RM 2,449.58</t>
+  </si>
+  <si>
+    <t>JWA9658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAMAHA 135LC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">134 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SPEED MANUAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FI SE </t>
+  </si>
+  <si>
+    <t>WXM86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA ALPHARD 2.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2493 </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">S C PACKAGE MY15 AGH30 FACELIFT </t>
+  </si>
+  <si>
+    <t>QCF9853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA - BOON SIEW </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA - BOON SIEW WAVE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">109 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S110 (KICK STARTER) </t>
+  </si>
+  <si>
+    <t>BNK7069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA - BOON SIEW EX5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DREAM 110 (ELECTRIC STARTER) </t>
+  </si>
+  <si>
+    <t>KAC24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford Ranger XL (A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1996 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT TRANSMISSION - 10 SP AUTOMATIC10 SP AUTOMATIC CONVENTIONAL6 SP AUTOMATIC CONVENTIONAL6 SP MANUAL CONVENTIONAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- SELECT VARIANT (SERIES) - XL MY22XLT MY22 </t>
+  </si>
+  <si>
+    <t>RM 3,500.40</t>
+  </si>
+  <si>
+    <t>RM 3,337.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory data missing </t>
+  </si>
+  <si>
+    <t>WDX2897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPHA 110 </t>
+  </si>
+  <si>
+    <t>PNP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota Alphard Exec Lounge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2494 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 SP AUTOMATIC CONSTANTLY VARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXECUTIVE LOUNGE MY23 </t>
+  </si>
+  <si>
+    <t>RM 7,984.73</t>
+  </si>
+  <si>
+    <t>KFP7077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCEDES-BENZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes Benz E350e A/L (CKD) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1999 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRONIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">350 E AMG LINE-MY24 W214 9 SP AUTOMATIC 9G </t>
+  </si>
+  <si>
+    <t>RM 9,990.14</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
     <t>Reason</t>
   </si>
   <si>
-    <t>VAJ124</t>
+    <t>BKD381</t>
   </si>
   <si>
     <t>NO_VEHICLE_INFO</t>
@@ -65,14 +380,86 @@
     <t>Unable to retrieve your vehicle information</t>
   </si>
   <si>
-    <t>VAH0124</t>
+    <t>QS9490E</t>
+  </si>
+  <si>
+    <t>FF9931</t>
+  </si>
+  <si>
+    <t>WPG31</t>
+  </si>
+  <si>
+    <t>AKF5409</t>
+  </si>
+  <si>
+    <t>VAY12</t>
+  </si>
+  <si>
+    <t>JUM89</t>
+  </si>
+  <si>
+    <t>SM5017</t>
+  </si>
+  <si>
+    <t>CEG9211</t>
+  </si>
+  <si>
+    <t>WA883Y</t>
+  </si>
+  <si>
+    <t>BCF1079</t>
+  </si>
+  <si>
+    <t>VMX6457</t>
+  </si>
+  <si>
+    <t>VGV6192</t>
+  </si>
+  <si>
+    <t>VCN1552</t>
+  </si>
+  <si>
+    <t>BRW3175</t>
+  </si>
+  <si>
+    <t>AEU6895</t>
+  </si>
+  <si>
+    <t>PRL3429</t>
+  </si>
+  <si>
+    <t>QTN4046</t>
+  </si>
+  <si>
+    <t>WXT3300</t>
+  </si>
+  <si>
+    <t>KDW3</t>
+  </si>
+  <si>
+    <t>KX8</t>
+  </si>
+  <si>
+    <t>WUH8456</t>
+  </si>
+  <si>
+    <t>WUG76</t>
+  </si>
+  <si>
+    <t>UITM2093</t>
+  </si>
+  <si>
+    <t>JXU6420</t>
+  </si>
+  <si>
+    <t>JXN8717</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -83,6 +470,10 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -115,11 +506,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -514,7 +906,1148 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" t="s">
+        <v>115</v>
+      </c>
+      <c r="H30" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -522,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -530,37 +2063,312 @@
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
+      <c r="B1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="77">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,121 +50,193 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>JXB2061</t>
+    <t>BHA2468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA HIACE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2986 </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">NA MY95 LH112 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takaful </t>
+  </si>
+  <si>
+    <t>Cover Type Third Party Fire &amp; Theft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM Sub Response Code E015 :Vehicle number or chassis number previously reported as Commercial Vehicle. </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 781.99</t>
+  </si>
+  <si>
+    <t>CCF5361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA INNOVA 2.0 E </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1998 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E MY05 AN40 </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t>RM 1,128.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>Cover Type Private Car (Enhanced)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail to call compliance link. Contact Your Marketer. </t>
+  </si>
+  <si>
+    <t>RM 1,044.90</t>
+  </si>
+  <si>
+    <t>QAB3377M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEXUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEXUS GS300 (A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUXURY MY24 EB10 </t>
+  </si>
+  <si>
+    <t>RM 7,582.55</t>
+  </si>
+  <si>
+    <t>RM 7,917.00</t>
+  </si>
+  <si>
+    <t>VDA9008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOLKSWAG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">035508 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1395 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGHLINE MY17 MK2 </t>
+  </si>
+  <si>
+    <t>RM 1,998.45</t>
+  </si>
+  <si>
+    <t>RM 1,869.63</t>
+  </si>
+  <si>
+    <t>WYX8315</t>
   </si>
   <si>
     <t xml:space="preserve">PERODUA </t>
   </si>
   <si>
-    <t xml:space="preserve">Perodua Axia 1000 X (CVT) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">998 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 SP AUTOMATIC CONSTANTLY VARI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">X MY23 D74A </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
-    <t>RM 972.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
-    <t>Cover Type Private Car (Enhanced)</t>
-  </si>
-  <si>
-    <t>RM 1,110.78</t>
-  </si>
-  <si>
-    <t>VNU9093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Alza AV (CVT) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1496 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC CONSTANTLY VARI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV MY22 </t>
-  </si>
-  <si>
-    <t>RM 1,436.11</t>
-  </si>
-  <si>
-    <t>RM 1,599.60</t>
-  </si>
-  <si>
-    <t>VHS5036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Axia 1000AV (A) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC CONVENTIONAL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV MY19 </t>
-  </si>
-  <si>
-    <t>RM 1,417.19</t>
-  </si>
-  <si>
-    <t>RM 1,545.40</t>
-  </si>
-  <si>
-    <t>SYX4879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Axia 1000 AV (CVT) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV MY23 D74A </t>
-  </si>
-  <si>
-    <t>RM 1,186.88</t>
-  </si>
-  <si>
-    <t>RM 1,298.93</t>
-  </si>
-  <si>
-    <t>SYX4841</t>
-  </si>
-  <si>
-    <t>RM 977.96</t>
-  </si>
-  <si>
-    <t>RM 1,098.63</t>
+    <t xml:space="preserve">PERODUA ALZA 1500 EZI(AUTO) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZI MY09 M500 </t>
+  </si>
+  <si>
+    <t>RM 1,103.78</t>
+  </si>
+  <si>
+    <t>RM 945.04</t>
+  </si>
+  <si>
+    <t>RM 851.89</t>
+  </si>
+  <si>
+    <t>RM 767.70</t>
+  </si>
+  <si>
+    <t>WVY6520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011 </t>
+  </si>
+  <si>
+    <t>RM 1,032.73</t>
+  </si>
+  <si>
+    <t>RM 910.13</t>
+  </si>
+  <si>
+    <t>RM 797.14</t>
+  </si>
+  <si>
+    <t>RM 743.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Alza 1.5 EZi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZi </t>
+  </si>
+  <si>
+    <t>RM 926.82</t>
   </si>
   <si>
     <t>Status</t>
@@ -570,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -688,36 +760,36 @@
         <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -726,286 +798,894 @@
         <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" t="s">
         <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
         <v>42</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
         <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
         <v>48</v>
       </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>50</v>
       </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" t="s">
+        <v>73</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1026,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="50">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,115 +50,85 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>WKR590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proton Waja 1.6(M) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2003 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1584 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 SP MANUAL </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">Takaful </t>
-  </si>
-  <si>
-    <t>Cover Type Third Party Fire &amp; Theft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEHICLE AGE EXCEEDED,VEHICLE AGE EXCEEDED </t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>WYY2299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAVAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haval H2 Comfort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1497 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 SP AUTOMATIC CONVENTIONAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMFORT (CKD) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>Cover Type Private Car (Enhanced)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>RM 1,767.30</t>
+  </si>
+  <si>
+    <t>PFE2883</t>
   </si>
   <si>
     <t xml:space="preserve">Zurich </t>
   </si>
   <si>
-    <t xml:space="preserve">System error, please contact IT support. </t>
-  </si>
-  <si>
-    <t>QAA8160F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERODUA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Myvi 1.3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1298 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 SP AUTOMATIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE ZHS </t>
-  </si>
-  <si>
     <t>Cover Type Comprehensive (1st party)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
-    <t>RM 918.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubb </t>
-  </si>
-  <si>
-    <t>Cover Type Private Car (Enhanced)</t>
-  </si>
-  <si>
-    <t>RM 1,078.89</t>
-  </si>
-  <si>
-    <t>RM 708.99</t>
-  </si>
-  <si>
-    <t>WWK7705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perodua Viva 1.0L Elite </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">989 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">-EJ VE </t>
-  </si>
-  <si>
-    <t>RM 705.26</t>
-  </si>
-  <si>
-    <t>RM 830.24</t>
-  </si>
-  <si>
-    <t>RM 517.33</t>
+    <t>RM 995.15</t>
+  </si>
+  <si>
+    <t>PNC2325</t>
+  </si>
+  <si>
+    <t>VPC3997</t>
+  </si>
+  <si>
+    <t>QSQ5120</t>
+  </si>
+  <si>
+    <t>BHR6643</t>
+  </si>
+  <si>
+    <t>VBW1332</t>
+  </si>
+  <si>
+    <t>WND7312</t>
+  </si>
+  <si>
+    <t>SMB9936</t>
+  </si>
+  <si>
+    <t>WNX3548</t>
+  </si>
+  <si>
+    <t>BPE2868</t>
+  </si>
+  <si>
+    <t>WQQ8293</t>
+  </si>
+  <si>
+    <t>VPA2184</t>
   </si>
   <si>
     <t>Status</t>
@@ -167,13 +137,31 @@
     <t>Reason</t>
   </si>
   <si>
-    <t>MU1977</t>
+    <t>AHG385</t>
   </si>
   <si>
     <t>NO_VEHICLE_INFO</t>
   </si>
   <si>
     <t>Unable to retrieve your vehicle information</t>
+  </si>
+  <si>
+    <t>QAL7209</t>
+  </si>
+  <si>
+    <t>NDM5588</t>
+  </si>
+  <si>
+    <t>WWX2121</t>
+  </si>
+  <si>
+    <t>ST830H</t>
+  </si>
+  <si>
+    <t>AHB7975</t>
+  </si>
+  <si>
+    <t>VLN738</t>
   </si>
 </sst>
 </file>
@@ -573,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -667,7 +655,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -688,7 +676,7 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
@@ -697,7 +685,7 @@
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
         <v>23</v>
@@ -705,139 +693,139 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
+      <c r="J4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
         <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -846,162 +834,162 @@
         <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="J8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
         <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L11" t="s">
         <v>23</v>
@@ -1009,66 +997,66 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
         <v>20</v>
@@ -1077,14 +1065,584 @@
         <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L13" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1092,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1105,21 +1663,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="176">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,40 +50,82 @@
     <t>Total Price</t>
   </si>
   <si>
-    <t>JKC9998</t>
+    <t>JVK1779</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA ADV150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">149 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE TRANSMISSION </t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle class does not match the class code </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokio Marine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your account has been blocked due to the existing policies issued are not being submitted for more than 10 days! </t>
+  </si>
+  <si>
+    <t>Cover Type Third Party Fire &amp; Theft</t>
+  </si>
+  <si>
+    <t>PRR5421</t>
   </si>
   <si>
     <t xml:space="preserve">HONDA </t>
   </si>
   <si>
-    <t xml:space="preserve">Honda Accord 2.4 VTi-L </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2007 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2354 </t>
+    <t xml:space="preserve">Honda City 1.5 (A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1497 </t>
   </si>
   <si>
     <t xml:space="preserve">5 SP AUTOMATIC </t>
   </si>
   <si>
-    <t xml:space="preserve">VTi-L FACELIFT </t>
+    <t xml:space="preserve">SE </t>
   </si>
   <si>
     <t xml:space="preserve">Takaful </t>
   </si>
   <si>
-    <t>Cover Type Comprehensive (1st party)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yes </t>
   </si>
   <si>
     <t xml:space="preserve">- </t>
   </si>
   <si>
-    <t>RM 1,326.76</t>
+    <t>RM 1,293.09</t>
   </si>
   <si>
     <t xml:space="preserve">Chubb </t>
@@ -92,46 +134,412 @@
     <t>Cover Type Private Car (Enhanced)</t>
   </si>
   <si>
-    <t>RM 1,580.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonpac </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No </t>
+    <t>RM 1,472.45</t>
+  </si>
+  <si>
+    <t>RM 1,178.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>RM 1,516.71</t>
+  </si>
+  <si>
+    <t>WB7932R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NISSAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan Almera 1.5E(A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1498 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 SP AUTOMATIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E (IMPUL) N17A15E </t>
+  </si>
+  <si>
+    <t>RM 1,564.16</t>
+  </si>
+  <si>
+    <t>WTX9642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Alza 1.5(A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZHP ADVANCED </t>
+  </si>
+  <si>
+    <t>RM 1,260.40</t>
+  </si>
+  <si>
+    <t>RM 1,062.70</t>
   </si>
   <si>
     <t xml:space="preserve">Failed Underwriting Vehicle Age </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokio Marine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your account has been blocked due to the existing policies issued are not being submitted for more than 10 days! </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurich </t>
-  </si>
-  <si>
-    <t>RM 1,496.80</t>
-  </si>
-  <si>
-    <t>Cover Type Third Party Fire &amp; Theft</t>
-  </si>
-  <si>
-    <t>RM 867.77</t>
-  </si>
-  <si>
-    <t>RM 774.93</t>
+    <t xml:space="preserve">Duplicate REFNO found. </t>
+  </si>
+  <si>
+    <t>RM 1,035.68</t>
+  </si>
+  <si>
+    <t>RM 824.50</t>
+  </si>
+  <si>
+    <t>RM 702.32</t>
+  </si>
+  <si>
+    <t>WEN7866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proton Iswara 1.3(M) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1996 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1298 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 SP MANUAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S C12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VEHICLE AGE EXCEEDED,VEHICLE AGE EXCEEDED </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referred due to Vehicle Sum Covered [2500] [BH ; RC ; Motor UW HQ] </t>
+  </si>
+  <si>
+    <t>MCH2151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan Almera 1.5V </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V N17A15V </t>
+  </si>
+  <si>
+    <t>RM 1,172.00</t>
+  </si>
+  <si>
+    <t>RM 1,346.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle use does not match the use code </t>
+  </si>
+  <si>
+    <t>RM 1,374.34</t>
+  </si>
+  <si>
+    <t>RM 797.14</t>
+  </si>
+  <si>
+    <t>RM 679.06</t>
+  </si>
+  <si>
+    <t>JSS9468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda Jazz 1.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 SP AUTOMATIC CONSTANTLY VARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V MY2014 FACELIFT </t>
+  </si>
+  <si>
+    <t>RM 1,970.42</t>
+  </si>
+  <si>
+    <t>RM 2,188.13</t>
+  </si>
+  <si>
+    <t>RM 1,951.88</t>
+  </si>
+  <si>
+    <t>RM 1,771.76</t>
+  </si>
+  <si>
+    <t>RW3512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proton Saga 1.3 CVT Standard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1332 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS VARIABLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STANDARD CVT MY2016 </t>
+  </si>
+  <si>
+    <t>RM 1,033.87</t>
+  </si>
+  <si>
+    <t>RM 1,250.88</t>
+  </si>
+  <si>
+    <t>RM 1,023.48</t>
+  </si>
+  <si>
+    <t>RM 1,311.86</t>
+  </si>
+  <si>
+    <t>RM 763.74</t>
+  </si>
+  <si>
+    <t>RM 648.41</t>
+  </si>
+  <si>
+    <t>BKN9186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota Vios 1.5J </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J-NCP93R BEPDKE </t>
+  </si>
+  <si>
+    <t>RM 1,050.50</t>
+  </si>
+  <si>
+    <t>RM 1,178.59</t>
+  </si>
+  <si>
+    <t>RM 1,184.52</t>
+  </si>
+  <si>
+    <t>RM 687.62</t>
+  </si>
+  <si>
+    <t>RM 654.51</t>
+  </si>
+  <si>
+    <t>JLY4743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proton Saga 1.3(M) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE LINE </t>
+  </si>
+  <si>
+    <t>RM 831.39</t>
+  </si>
+  <si>
+    <t>RM 875.53</t>
+  </si>
+  <si>
+    <t>RM 841.92</t>
+  </si>
+  <si>
+    <t>RM 489.96</t>
+  </si>
+  <si>
+    <t>RM 561.96</t>
+  </si>
+  <si>
+    <t>VBY8385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda Civic 1.8 S </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1799 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S </t>
+  </si>
+  <si>
+    <t>RM 2,426.90</t>
+  </si>
+  <si>
+    <t>RM 2,724.68</t>
+  </si>
+  <si>
+    <t>RM 2,441.21</t>
+  </si>
+  <si>
+    <t>RM 2,597.76</t>
+  </si>
+  <si>
+    <t>JPK5366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZi PREMIUM </t>
+  </si>
+  <si>
+    <t>RM 1,042.05</t>
+  </si>
+  <si>
+    <t>RM 1,211.37</t>
+  </si>
+  <si>
+    <t>RM 949.86</t>
+  </si>
+  <si>
+    <t>RM 1,269.02</t>
+  </si>
+  <si>
+    <t>RM 708.99</t>
+  </si>
+  <si>
+    <t>RM 631.59</t>
+  </si>
+  <si>
+    <t>JGC7679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan Cefiro Excimo 2.0V6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1995 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXCIMO L A32 </t>
+  </si>
+  <si>
+    <t>RM 641.03</t>
+  </si>
+  <si>
+    <t>VPF1134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAMAHA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAMAHA Y15ZR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 SPEED MANUAL </t>
+  </si>
+  <si>
+    <t>RM 645.68</t>
+  </si>
+  <si>
+    <t>VCK772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan Navara 2.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2488 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALIBRE </t>
+  </si>
+  <si>
+    <t>RM 1,356.90</t>
+  </si>
+  <si>
+    <t>RM 1,454.86</t>
+  </si>
+  <si>
+    <t>RM 1,652.55</t>
+  </si>
+  <si>
+    <t>RM 922.53</t>
+  </si>
+  <si>
+    <t>RM 820.46</t>
+  </si>
+  <si>
+    <t>VDS5747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Bezza 1300 X (A) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1329 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM X </t>
+  </si>
+  <si>
+    <t>RM 1,405.23</t>
+  </si>
+  <si>
+    <t>RM 1,614.17</t>
+  </si>
+  <si>
+    <t>RM 1,391.61</t>
+  </si>
+  <si>
+    <t>RM 1,518.08</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
     <t>Reason</t>
+  </si>
+  <si>
+    <t>VMM949</t>
+  </si>
+  <si>
+    <t>NO_VEHICLE_INFO</t>
+  </si>
+  <si>
+    <t>Unable to retrieve your vehicle information</t>
   </si>
 </sst>
 </file>
@@ -531,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -649,16 +1057,16 @@
         <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -684,175 +1092,3671 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>80</v>
+      </c>
+      <c r="L26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" t="s">
+        <v>38</v>
+      </c>
+      <c r="I32" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" t="s">
+        <v>57</v>
+      </c>
+      <c r="H35" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" t="s">
+        <v>49</v>
+      </c>
+      <c r="G36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H37" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" t="s">
+        <v>88</v>
+      </c>
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K40" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" t="s">
+        <v>87</v>
+      </c>
+      <c r="G41" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" t="s">
+        <v>87</v>
+      </c>
+      <c r="G42" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" t="s">
+        <v>96</v>
+      </c>
+      <c r="G43" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" t="s">
+        <v>38</v>
+      </c>
+      <c r="I44" t="s">
+        <v>39</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F45" t="s">
+        <v>96</v>
+      </c>
+      <c r="G45" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46" t="s">
+        <v>96</v>
+      </c>
+      <c r="G46" t="s">
+        <v>97</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H47" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" t="s">
+        <v>95</v>
+      </c>
+      <c r="F48" t="s">
+        <v>96</v>
+      </c>
+      <c r="G48" t="s">
+        <v>97</v>
+      </c>
+      <c r="H48" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K49" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>49</v>
+      </c>
+      <c r="G50" t="s">
+        <v>108</v>
+      </c>
+      <c r="H50" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" t="s">
+        <v>107</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" t="s">
+        <v>108</v>
+      </c>
+      <c r="H51" t="s">
+        <v>38</v>
+      </c>
+      <c r="I51" t="s">
+        <v>39</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" t="s">
+        <v>49</v>
+      </c>
+      <c r="G52" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s">
+        <v>60</v>
+      </c>
+      <c r="L52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" t="s">
+        <v>49</v>
+      </c>
+      <c r="G53" t="s">
+        <v>108</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" t="s">
+        <v>108</v>
+      </c>
+      <c r="H54" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K54" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G55" t="s">
+        <v>108</v>
+      </c>
+      <c r="H55" t="s">
+        <v>34</v>
+      </c>
+      <c r="I55" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" t="s">
+        <v>49</v>
+      </c>
+      <c r="G56" t="s">
+        <v>108</v>
+      </c>
+      <c r="H56" t="s">
+        <v>42</v>
+      </c>
+      <c r="I56" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" t="s">
+        <v>116</v>
+      </c>
+      <c r="E57" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" t="s">
+        <v>70</v>
+      </c>
+      <c r="G57" t="s">
+        <v>117</v>
+      </c>
+      <c r="H57" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" t="s">
+        <v>70</v>
+      </c>
+      <c r="G58" t="s">
+        <v>117</v>
+      </c>
+      <c r="H58" t="s">
+        <v>38</v>
+      </c>
+      <c r="I58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" t="s">
+        <v>95</v>
+      </c>
+      <c r="F59" t="s">
+        <v>70</v>
+      </c>
+      <c r="G59" t="s">
+        <v>117</v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>60</v>
+      </c>
+      <c r="L59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" t="s">
+        <v>95</v>
+      </c>
+      <c r="F60" t="s">
+        <v>70</v>
+      </c>
+      <c r="G60" t="s">
+        <v>117</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" t="s">
+        <v>70</v>
+      </c>
+      <c r="G61" t="s">
+        <v>117</v>
+      </c>
+      <c r="H61" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K61" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D62" t="s">
+        <v>116</v>
+      </c>
+      <c r="E62" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" t="s">
+        <v>70</v>
+      </c>
+      <c r="G62" t="s">
+        <v>117</v>
+      </c>
+      <c r="H62" t="s">
+        <v>34</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" t="s">
+        <v>115</v>
+      </c>
+      <c r="D63" t="s">
+        <v>116</v>
+      </c>
+      <c r="E63" t="s">
+        <v>95</v>
+      </c>
+      <c r="F63" t="s">
+        <v>70</v>
+      </c>
+      <c r="G63" t="s">
+        <v>117</v>
+      </c>
+      <c r="H63" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K63" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" t="s">
+        <v>86</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
+        <v>96</v>
+      </c>
+      <c r="G64" t="s">
+        <v>126</v>
+      </c>
+      <c r="H64" t="s">
+        <v>34</v>
+      </c>
+      <c r="I64" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K64" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>124</v>
+      </c>
+      <c r="D65" t="s">
+        <v>86</v>
+      </c>
+      <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
+        <v>96</v>
+      </c>
+      <c r="G65" t="s">
+        <v>126</v>
+      </c>
+      <c r="H65" t="s">
+        <v>38</v>
+      </c>
+      <c r="I65" t="s">
+        <v>39</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K65" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" t="s">
+        <v>86</v>
+      </c>
+      <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
+        <v>96</v>
+      </c>
+      <c r="G66" t="s">
+        <v>126</v>
+      </c>
+      <c r="H66" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>123</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" t="s">
+        <v>86</v>
+      </c>
+      <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" t="s">
+        <v>126</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
+        <v>96</v>
+      </c>
+      <c r="G68" t="s">
+        <v>126</v>
+      </c>
+      <c r="H68" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K68" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" t="s">
+        <v>69</v>
+      </c>
+      <c r="F69" t="s">
+        <v>49</v>
+      </c>
+      <c r="G69" t="s">
+        <v>133</v>
+      </c>
+      <c r="H69" t="s">
+        <v>34</v>
+      </c>
+      <c r="I69" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K69" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" t="s">
+        <v>132</v>
+      </c>
+      <c r="D70" t="s">
+        <v>76</v>
+      </c>
+      <c r="E70" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" t="s">
+        <v>133</v>
+      </c>
+      <c r="H70" t="s">
+        <v>38</v>
+      </c>
+      <c r="I70" t="s">
+        <v>39</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K70" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" t="s">
+        <v>69</v>
+      </c>
+      <c r="F71" t="s">
+        <v>49</v>
+      </c>
+      <c r="G71" t="s">
+        <v>133</v>
+      </c>
+      <c r="H71" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K71" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>131</v>
+      </c>
+      <c r="B72" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" t="s">
+        <v>76</v>
+      </c>
+      <c r="E72" t="s">
+        <v>69</v>
+      </c>
+      <c r="F72" t="s">
+        <v>49</v>
+      </c>
+      <c r="G72" t="s">
+        <v>133</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73" t="s">
+        <v>69</v>
+      </c>
+      <c r="F73" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73" t="s">
+        <v>133</v>
+      </c>
+      <c r="H73" t="s">
+        <v>42</v>
+      </c>
+      <c r="I73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K73" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>131</v>
+      </c>
+      <c r="B74" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" t="s">
+        <v>76</v>
+      </c>
+      <c r="E74" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" t="s">
+        <v>133</v>
+      </c>
+      <c r="H74" t="s">
+        <v>34</v>
+      </c>
+      <c r="I74" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K74" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" t="s">
+        <v>76</v>
+      </c>
+      <c r="E75" t="s">
+        <v>69</v>
+      </c>
+      <c r="F75" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" t="s">
+        <v>133</v>
+      </c>
+      <c r="H75" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K75" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" t="s">
+        <v>141</v>
+      </c>
+      <c r="D76" t="s">
+        <v>142</v>
+      </c>
+      <c r="E76" t="s">
+        <v>143</v>
+      </c>
+      <c r="F76" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" t="s">
+        <v>144</v>
+      </c>
+      <c r="H76" t="s">
+        <v>34</v>
+      </c>
+      <c r="I76" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s">
+        <v>72</v>
+      </c>
+      <c r="L76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" t="s">
+        <v>141</v>
+      </c>
+      <c r="D77" t="s">
+        <v>142</v>
+      </c>
+      <c r="E77" t="s">
+        <v>143</v>
+      </c>
+      <c r="F77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G77" t="s">
+        <v>144</v>
+      </c>
+      <c r="H77" t="s">
+        <v>42</v>
+      </c>
+      <c r="I77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K77" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>114</v>
+      </c>
+      <c r="B78" t="s">
+        <v>66</v>
+      </c>
+      <c r="C78" t="s">
+        <v>115</v>
+      </c>
+      <c r="D78" t="s">
+        <v>116</v>
+      </c>
+      <c r="E78" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" t="s">
+        <v>70</v>
+      </c>
+      <c r="G78" t="s">
+        <v>117</v>
+      </c>
+      <c r="H78" t="s">
+        <v>34</v>
+      </c>
+      <c r="I78" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K78" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" t="s">
+        <v>66</v>
+      </c>
+      <c r="C79" t="s">
+        <v>115</v>
+      </c>
+      <c r="D79" t="s">
+        <v>116</v>
+      </c>
+      <c r="E79" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79" t="s">
+        <v>70</v>
+      </c>
+      <c r="G79" t="s">
+        <v>117</v>
+      </c>
+      <c r="H79" t="s">
+        <v>38</v>
+      </c>
+      <c r="I79" t="s">
+        <v>39</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K79" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" t="s">
+        <v>66</v>
+      </c>
+      <c r="C80" t="s">
+        <v>115</v>
+      </c>
+      <c r="D80" t="s">
+        <v>116</v>
+      </c>
+      <c r="E80" t="s">
+        <v>95</v>
+      </c>
+      <c r="F80" t="s">
+        <v>70</v>
+      </c>
+      <c r="G80" t="s">
+        <v>117</v>
+      </c>
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s">
+        <v>60</v>
+      </c>
+      <c r="L80" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>114</v>
+      </c>
+      <c r="B81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C81" t="s">
+        <v>115</v>
+      </c>
+      <c r="D81" t="s">
+        <v>116</v>
+      </c>
+      <c r="E81" t="s">
+        <v>95</v>
+      </c>
+      <c r="F81" t="s">
+        <v>70</v>
+      </c>
+      <c r="G81" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>114</v>
+      </c>
+      <c r="B82" t="s">
+        <v>66</v>
+      </c>
+      <c r="C82" t="s">
+        <v>115</v>
+      </c>
+      <c r="D82" t="s">
+        <v>116</v>
+      </c>
+      <c r="E82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" t="s">
+        <v>70</v>
+      </c>
+      <c r="G82" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K82" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>114</v>
+      </c>
+      <c r="B83" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" t="s">
+        <v>116</v>
+      </c>
+      <c r="E83" t="s">
+        <v>95</v>
+      </c>
+      <c r="F83" t="s">
+        <v>70</v>
+      </c>
+      <c r="G83" t="s">
+        <v>117</v>
+      </c>
+      <c r="H83" t="s">
+        <v>34</v>
+      </c>
+      <c r="I83" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K83" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>114</v>
+      </c>
+      <c r="B84" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" t="s">
+        <v>115</v>
+      </c>
+      <c r="D84" t="s">
+        <v>116</v>
+      </c>
+      <c r="E84" t="s">
+        <v>95</v>
+      </c>
+      <c r="F84" t="s">
+        <v>70</v>
+      </c>
+      <c r="G84" t="s">
+        <v>117</v>
+      </c>
+      <c r="H84" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" t="s">
+        <v>26</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K84" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>146</v>
+      </c>
+      <c r="B85" t="s">
+        <v>147</v>
+      </c>
+      <c r="C85" t="s">
+        <v>148</v>
+      </c>
+      <c r="D85" t="s">
+        <v>149</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>150</v>
+      </c>
+      <c r="G85" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K85" t="s">
         <v>22</v>
       </c>
-      <c r="L8" t="s">
-        <v>37</v>
+      <c r="L85" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" t="s">
+        <v>148</v>
+      </c>
+      <c r="D86" t="s">
+        <v>149</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>150</v>
+      </c>
+      <c r="G86" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K86" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87" t="s">
+        <v>148</v>
+      </c>
+      <c r="D87" t="s">
+        <v>149</v>
+      </c>
+      <c r="E87" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" t="s">
+        <v>150</v>
+      </c>
+      <c r="G87" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" t="s">
+        <v>24</v>
+      </c>
+      <c r="I87" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K87" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" t="s">
+        <v>147</v>
+      </c>
+      <c r="C88" t="s">
+        <v>148</v>
+      </c>
+      <c r="D88" t="s">
+        <v>149</v>
+      </c>
+      <c r="E88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" t="s">
+        <v>150</v>
+      </c>
+      <c r="G88" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K88" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" t="s">
+        <v>153</v>
+      </c>
+      <c r="D89" t="s">
+        <v>154</v>
+      </c>
+      <c r="E89" t="s">
+        <v>155</v>
+      </c>
+      <c r="F89" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89" t="s">
+        <v>156</v>
+      </c>
+      <c r="H89" t="s">
+        <v>34</v>
+      </c>
+      <c r="I89" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" t="s">
+        <v>45</v>
+      </c>
+      <c r="C90" t="s">
+        <v>153</v>
+      </c>
+      <c r="D90" t="s">
+        <v>154</v>
+      </c>
+      <c r="E90" t="s">
+        <v>155</v>
+      </c>
+      <c r="F90" t="s">
+        <v>32</v>
+      </c>
+      <c r="G90" t="s">
+        <v>156</v>
+      </c>
+      <c r="H90" t="s">
+        <v>38</v>
+      </c>
+      <c r="I90" t="s">
+        <v>39</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K90" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>152</v>
+      </c>
+      <c r="B91" t="s">
+        <v>45</v>
+      </c>
+      <c r="C91" t="s">
+        <v>153</v>
+      </c>
+      <c r="D91" t="s">
+        <v>154</v>
+      </c>
+      <c r="E91" t="s">
+        <v>155</v>
+      </c>
+      <c r="F91" t="s">
+        <v>32</v>
+      </c>
+      <c r="G91" t="s">
+        <v>156</v>
+      </c>
+      <c r="H91" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s">
+        <v>80</v>
+      </c>
+      <c r="L91" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>152</v>
+      </c>
+      <c r="B92" t="s">
+        <v>45</v>
+      </c>
+      <c r="C92" t="s">
+        <v>153</v>
+      </c>
+      <c r="D92" t="s">
+        <v>154</v>
+      </c>
+      <c r="E92" t="s">
+        <v>155</v>
+      </c>
+      <c r="F92" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92" t="s">
+        <v>156</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" t="s">
+        <v>153</v>
+      </c>
+      <c r="D93" t="s">
+        <v>154</v>
+      </c>
+      <c r="E93" t="s">
+        <v>155</v>
+      </c>
+      <c r="F93" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" t="s">
+        <v>156</v>
+      </c>
+      <c r="H93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I93" t="s">
+        <v>20</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K93" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>152</v>
+      </c>
+      <c r="B94" t="s">
+        <v>45</v>
+      </c>
+      <c r="C94" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94" t="s">
+        <v>154</v>
+      </c>
+      <c r="E94" t="s">
+        <v>155</v>
+      </c>
+      <c r="F94" t="s">
+        <v>32</v>
+      </c>
+      <c r="G94" t="s">
+        <v>156</v>
+      </c>
+      <c r="H94" t="s">
+        <v>34</v>
+      </c>
+      <c r="I94" t="s">
+        <v>26</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K94" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>152</v>
+      </c>
+      <c r="B95" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" t="s">
+        <v>153</v>
+      </c>
+      <c r="D95" t="s">
+        <v>154</v>
+      </c>
+      <c r="E95" t="s">
+        <v>155</v>
+      </c>
+      <c r="F95" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" t="s">
+        <v>156</v>
+      </c>
+      <c r="H95" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" t="s">
+        <v>26</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K95" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>162</v>
+      </c>
+      <c r="B96" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" t="s">
+        <v>164</v>
+      </c>
+      <c r="E96" t="s">
+        <v>165</v>
+      </c>
+      <c r="F96" t="s">
+        <v>49</v>
+      </c>
+      <c r="G96" t="s">
+        <v>166</v>
+      </c>
+      <c r="H96" t="s">
+        <v>34</v>
+      </c>
+      <c r="I96" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K96" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>162</v>
+      </c>
+      <c r="B97" t="s">
+        <v>53</v>
+      </c>
+      <c r="C97" t="s">
+        <v>163</v>
+      </c>
+      <c r="D97" t="s">
+        <v>164</v>
+      </c>
+      <c r="E97" t="s">
+        <v>165</v>
+      </c>
+      <c r="F97" t="s">
+        <v>49</v>
+      </c>
+      <c r="G97" t="s">
+        <v>166</v>
+      </c>
+      <c r="H97" t="s">
+        <v>38</v>
+      </c>
+      <c r="I97" t="s">
+        <v>39</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K97" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>162</v>
+      </c>
+      <c r="B98" t="s">
+        <v>53</v>
+      </c>
+      <c r="C98" t="s">
+        <v>163</v>
+      </c>
+      <c r="D98" t="s">
+        <v>164</v>
+      </c>
+      <c r="E98" t="s">
+        <v>165</v>
+      </c>
+      <c r="F98" t="s">
+        <v>49</v>
+      </c>
+      <c r="G98" t="s">
+        <v>166</v>
+      </c>
+      <c r="H98" t="s">
+        <v>19</v>
+      </c>
+      <c r="I98" t="s">
+        <v>20</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K98" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99" t="s">
+        <v>163</v>
+      </c>
+      <c r="D99" t="s">
+        <v>164</v>
+      </c>
+      <c r="E99" t="s">
+        <v>165</v>
+      </c>
+      <c r="F99" t="s">
+        <v>49</v>
+      </c>
+      <c r="G99" t="s">
+        <v>166</v>
+      </c>
+      <c r="H99" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99" t="s">
+        <v>20</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s">
+        <v>25</v>
+      </c>
+      <c r="L99" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" t="s">
+        <v>53</v>
+      </c>
+      <c r="C100" t="s">
+        <v>163</v>
+      </c>
+      <c r="D100" t="s">
+        <v>164</v>
+      </c>
+      <c r="E100" t="s">
+        <v>165</v>
+      </c>
+      <c r="F100" t="s">
+        <v>49</v>
+      </c>
+      <c r="G100" t="s">
+        <v>166</v>
+      </c>
+      <c r="H100" t="s">
+        <v>42</v>
+      </c>
+      <c r="I100" t="s">
+        <v>20</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K100" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L100"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -860,7 +4764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -873,10 +4777,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>39</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eauto-insurance/output-results.xlsx
+++ b/scripts/eauto-insurance/output-results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>Vehicle Number</t>
   </si>
@@ -50,26 +50,62 @@
     <t>Total Price</t>
   </si>
   <si>
+    <t>VPM7358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERODUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perodua Myvi 1500 AV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1496 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 SP AUTOMATIC CONSTANTLY VARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV MY17 FACELIFT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb </t>
+  </si>
+  <si>
+    <t>Cover Type Private Car (Enhanced)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sum Insured more than -8.51 % below market value is Decline Risk.] </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonpac </t>
+  </si>
+  <si>
+    <t>Cover Type Comprehensive (1st party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle class does not match the class code </t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
     <t>Reason</t>
-  </si>
-  <si>
-    <t>VPM7358</t>
-  </si>
-  <si>
-    <t>NO_VEHICLE_INFO</t>
-  </si>
-  <si>
-    <t>Unable to retrieve your vehicle information</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -80,6 +116,10 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -112,11 +152,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -457,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -511,7 +552,84 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -519,7 +637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -527,26 +645,15 @@
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
+      <c r="B1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
